--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.24697417703696</v>
+        <v>8.815133303768507</v>
       </c>
       <c r="D2" t="n">
-        <v>54.07790891039396</v>
+        <v>8.787660197939019</v>
       </c>
       <c r="E2" t="n">
-        <v>19.58458051941917</v>
+        <v>3.182494334405616</v>
       </c>
       <c r="F2" t="n">
-        <v>19.58673009142379</v>
+        <v>3.182843639856366</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.37638677775671</v>
+        <v>8.836162851385467</v>
       </c>
       <c r="D3" t="n">
-        <v>54.70561087124209</v>
+        <v>8.88966176657684</v>
       </c>
       <c r="E3" t="n">
-        <v>19.58458051941917</v>
+        <v>3.182494334405616</v>
       </c>
       <c r="F3" t="n">
-        <v>19.58673009142379</v>
+        <v>3.182843639856366</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.72639538434986</v>
+        <v>2.880539249956853</v>
       </c>
       <c r="D4" t="n">
-        <v>17.90353221334749</v>
+        <v>2.909323984668968</v>
       </c>
       <c r="E4" t="n">
-        <v>19.58458051941917</v>
+        <v>3.182494334405616</v>
       </c>
       <c r="F4" t="n">
-        <v>19.58673009142379</v>
+        <v>3.182843639856366</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.86155178758844</v>
+        <v>2.090002165483121</v>
       </c>
       <c r="D5" t="n">
-        <v>12.86307019421715</v>
+        <v>2.090248906560288</v>
       </c>
       <c r="E5" t="n">
-        <v>19.58458051941917</v>
+        <v>3.182494334405616</v>
       </c>
       <c r="F5" t="n">
-        <v>19.58673009142379</v>
+        <v>3.182843639856366</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
